--- a/artfynd/A 64461-2020 artfynd.xlsx
+++ b/artfynd/A 64461-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64461-2020 artfynd.xlsx
+++ b/artfynd/A 64461-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6993,10 +6993,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112606043</v>
+        <v>112610217</v>
       </c>
       <c r="B56" t="n">
-        <v>77527</v>
+        <v>88855</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7009,34 +7009,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715550</v>
+        <v>715567</v>
       </c>
       <c r="R56" t="n">
-        <v>7158012</v>
+        <v>7158034</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112606036</v>
+        <v>112610203</v>
       </c>
       <c r="B57" t="n">
-        <v>91220</v>
+        <v>78448</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7116,34 +7116,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715537</v>
+        <v>715438</v>
       </c>
       <c r="R57" t="n">
-        <v>7157949</v>
+        <v>7157851</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7207,10 +7207,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112610217</v>
+        <v>112610216</v>
       </c>
       <c r="B58" t="n">
-        <v>88855</v>
+        <v>78448</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7223,21 +7223,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715567</v>
+        <v>715547</v>
       </c>
       <c r="R58" t="n">
-        <v>7158034</v>
+        <v>7158049</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112606033</v>
+        <v>112610215</v>
       </c>
       <c r="B59" t="n">
-        <v>89924</v>
+        <v>77608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7326,38 +7326,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715488</v>
+        <v>715552</v>
       </c>
       <c r="R59" t="n">
-        <v>7157979</v>
+        <v>7158032</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7421,10 +7421,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112610203</v>
+        <v>112610207</v>
       </c>
       <c r="B60" t="n">
-        <v>78448</v>
+        <v>89924</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7433,25 +7433,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715438</v>
+        <v>715495</v>
       </c>
       <c r="R60" t="n">
-        <v>7157851</v>
+        <v>7157984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7528,10 +7528,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112610214</v>
+        <v>112610208</v>
       </c>
       <c r="B61" t="n">
-        <v>77527</v>
+        <v>91220</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7544,21 +7544,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715554</v>
+        <v>715538</v>
       </c>
       <c r="R61" t="n">
-        <v>7158013</v>
+        <v>7157953</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7635,10 +7635,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112610211</v>
+        <v>112610212</v>
       </c>
       <c r="B62" t="n">
-        <v>77527</v>
+        <v>91032</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7647,25 +7647,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715544</v>
+        <v>715538</v>
       </c>
       <c r="R62" t="n">
-        <v>7157977</v>
+        <v>7158021</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7742,10 +7742,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112610216</v>
+        <v>112610218</v>
       </c>
       <c r="B63" t="n">
-        <v>78448</v>
+        <v>77608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7758,21 +7758,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715547</v>
+        <v>715595</v>
       </c>
       <c r="R63" t="n">
-        <v>7158049</v>
+        <v>7158074</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7849,10 +7849,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112606044</v>
+        <v>112610204</v>
       </c>
       <c r="B64" t="n">
-        <v>77608</v>
+        <v>78953</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7861,38 +7861,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715554</v>
+        <v>715470</v>
       </c>
       <c r="R64" t="n">
-        <v>7158033</v>
+        <v>7157919</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7956,10 +7956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112606042</v>
+        <v>112610202</v>
       </c>
       <c r="B65" t="n">
-        <v>77527</v>
+        <v>77609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7972,34 +7972,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715536</v>
+        <v>715439</v>
       </c>
       <c r="R65" t="n">
-        <v>7158021</v>
+        <v>7157849</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112606022</v>
+        <v>112610206</v>
       </c>
       <c r="B66" t="n">
         <v>91032</v>
@@ -8099,14 +8099,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715435</v>
+        <v>715520</v>
       </c>
       <c r="R66" t="n">
-        <v>7157793</v>
+        <v>7157969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8170,10 +8170,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112606046</v>
+        <v>112610209</v>
       </c>
       <c r="B67" t="n">
-        <v>88855</v>
+        <v>77527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8186,34 +8186,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Slipstensjön, Vb</t>
+          <t>Gladaberg, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715568</v>
+        <v>715535</v>
       </c>
       <c r="R67" t="n">
-        <v>7158031</v>
+        <v>7157949</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112610215</v>
+        <v>112610213</v>
       </c>
       <c r="B68" t="n">
-        <v>77608</v>
+        <v>77527</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8293,21 +8293,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715552</v>
+        <v>715534</v>
       </c>
       <c r="R68" t="n">
-        <v>7158032</v>
+        <v>7158019</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8384,10 +8384,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112610207</v>
+        <v>112610200</v>
       </c>
       <c r="B69" t="n">
-        <v>89924</v>
+        <v>5473</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8396,25 +8396,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>101410</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715495</v>
+        <v>715453</v>
       </c>
       <c r="R69" t="n">
-        <v>7157984</v>
+        <v>7157854</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8488,4072 +8488,6 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>112606049</v>
-      </c>
-      <c r="B70" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>715588</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7158083</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>112606030</v>
-      </c>
-      <c r="B71" t="n">
-        <v>78953</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>715473</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7157926</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>112606045</v>
-      </c>
-      <c r="B72" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>715547</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7158046</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>112606041</v>
-      </c>
-      <c r="B73" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>715543</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7158020</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>112606023</v>
-      </c>
-      <c r="B74" t="n">
-        <v>77609</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>715441</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7157852</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>112606040</v>
-      </c>
-      <c r="B75" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>353</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>715544</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7157975</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>112606035</v>
-      </c>
-      <c r="B76" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>715550</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7157948</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>112606014</v>
-      </c>
-      <c r="B77" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>715603</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7158096</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>112606031</v>
-      </c>
-      <c r="B78" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>715493</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7157931</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>112606037</v>
-      </c>
-      <c r="B79" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>353</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>715532</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7157949</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>112610208</v>
-      </c>
-      <c r="B80" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Nordtagging</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Odonticium romellii</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>715538</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7157953</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>112606017</v>
-      </c>
-      <c r="B81" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>715428</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7157906</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>112606025</v>
-      </c>
-      <c r="B82" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>715438</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7157828</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>112606021</v>
-      </c>
-      <c r="B83" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>715413</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7157792</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>112610201</v>
-      </c>
-      <c r="B84" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>715464</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7157837</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>112610212</v>
-      </c>
-      <c r="B85" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>715538</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7158021</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>112606019</v>
-      </c>
-      <c r="B86" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>715456</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7157855</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>112606029</v>
-      </c>
-      <c r="B87" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>715430</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7157902</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>112610210</v>
-      </c>
-      <c r="B88" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>715543</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7157976</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>112606027</v>
-      </c>
-      <c r="B89" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>715393</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7157836</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>112606039</v>
-      </c>
-      <c r="B90" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>715548</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7157979</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>112606038</v>
-      </c>
-      <c r="B91" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>715536</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7157977</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>112610218</v>
-      </c>
-      <c r="B92" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>715595</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7158074</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>112606032</v>
-      </c>
-      <c r="B93" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>715492</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7157984</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>112610204</v>
-      </c>
-      <c r="B94" t="n">
-        <v>78953</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>715470</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7157919</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>112606024</v>
-      </c>
-      <c r="B95" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>715439</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7157850</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>112606018</v>
-      </c>
-      <c r="B96" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>715427</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7157875</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>112606028</v>
-      </c>
-      <c r="B97" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>715411</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7157884</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>112606015</v>
-      </c>
-      <c r="B98" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>715499</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7157920</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>112610202</v>
-      </c>
-      <c r="B99" t="n">
-        <v>77609</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>715439</v>
-      </c>
-      <c r="R99" t="n">
-        <v>7157849</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>112606047</v>
-      </c>
-      <c r="B100" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>715593</v>
-      </c>
-      <c r="R100" t="n">
-        <v>7158072</v>
-      </c>
-      <c r="S100" t="n">
-        <v>10</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>112610206</v>
-      </c>
-      <c r="B101" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>715520</v>
-      </c>
-      <c r="R101" t="n">
-        <v>7157969</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>112610209</v>
-      </c>
-      <c r="B102" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>353</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q102" t="n">
-        <v>715535</v>
-      </c>
-      <c r="R102" t="n">
-        <v>7157949</v>
-      </c>
-      <c r="S102" t="n">
-        <v>10</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="inlineStr"/>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>112606020</v>
-      </c>
-      <c r="B103" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q103" t="n">
-        <v>715462</v>
-      </c>
-      <c r="R103" t="n">
-        <v>7157841</v>
-      </c>
-      <c r="S103" t="n">
-        <v>10</v>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT103" t="inlineStr"/>
-      <c r="AW103" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>112610213</v>
-      </c>
-      <c r="B104" t="n">
-        <v>77527</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>353</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q104" t="n">
-        <v>715534</v>
-      </c>
-      <c r="R104" t="n">
-        <v>7158019</v>
-      </c>
-      <c r="S104" t="n">
-        <v>10</v>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT104" t="inlineStr"/>
-      <c r="AW104" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>112606034</v>
-      </c>
-      <c r="B105" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q105" t="n">
-        <v>715516</v>
-      </c>
-      <c r="R105" t="n">
-        <v>7157937</v>
-      </c>
-      <c r="S105" t="n">
-        <v>10</v>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT105" t="inlineStr"/>
-      <c r="AW105" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>112606026</v>
-      </c>
-      <c r="B106" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q106" t="n">
-        <v>715409</v>
-      </c>
-      <c r="R106" t="n">
-        <v>7157803</v>
-      </c>
-      <c r="S106" t="n">
-        <v>10</v>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT106" t="inlineStr"/>
-      <c r="AW106" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>112610200</v>
-      </c>
-      <c r="B107" t="n">
-        <v>5473</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Nothorhina muricata</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Gladaberg, Vb</t>
-        </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>715453</v>
-      </c>
-      <c r="R107" t="n">
-        <v>7157854</v>
-      </c>
-      <c r="S107" t="n">
-        <v>10</v>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="inlineStr"/>
-      <c r="AW107" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
